--- a/backend/timetable.xlsx
+++ b/backend/timetable.xlsx
@@ -7,8 +7,20 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Mrs.Chithra" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mrs.Nathiya" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="T-servanthi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="T-Hemanand" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="T-Subha" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="T-Keerthana" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="T-chithra" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="T-Vaishnavi" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="T-Reena" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="T-Nathiya" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="T-Sulochana" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="T-Savija" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="T-Illamchezhia" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="T-Shanmugam" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="C-3A" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="C-3B" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,27 +482,367 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AAI
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DV LAB
 (3A)
 [LAB]</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AAI
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DV LAB
 (3A)
 [LAB]</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AAI
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DV LAB
 (3A)
 [LAB]</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DV
+(3A)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DV
+(3A)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DV
+(3A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DV
+(3A)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DV
+(3A)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DV
+(3B)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DV
+(3B)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DV LAB
+(3B)
+[LAB]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DV LAB
+(3B)
+[LAB]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DV LAB
+(3B)
+[LAB]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DV
+(3B)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DV
+(3B)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DV
+(3B)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -506,12 +858,173 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AAI
-(3A)</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ASL
+(3B)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASL
+(3B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ASL
+(3B)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ASL
+(3B)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASL
+(3B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ASL
+(3B)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -523,12 +1036,7 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AAI
-(3A)</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -549,12 +1057,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AAI
-(3A)</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -565,22 +1068,520 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AAI
-(3A)</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AAI
-(3A)</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DV LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DV LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DV LAB
+[LAB]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AAI LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AAI LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AAI LAB
+[LAB]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DV LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DV LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DV LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AAI LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AAI LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AAI LAB
+[LAB]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AAI</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -653,27 +1654,9 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AAI
-(3B)
-[LAB]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>AAI
-(3B)
-[LAB]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>AAI
-(3B)
-[LAB]</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -687,12 +1670,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AAI
-(3B)</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -717,28 +1695,13 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AAI
-(3B)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AAI
-(3B)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AAI
-(3B)</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -747,24 +1710,1142 @@
           <t>Fri</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AAI
-(3B)</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AAI
+(3A)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AAI
+(3A)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AAI LAB
+(3A)
+[LAB]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AAI LAB
+(3A)
+[LAB]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AAI LAB
+(3A)
+[LAB]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AAI
+(3A)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AAI
+(3A)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>AAI
+(3A)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CV
+(3A)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CV
+(3A)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CV
+(3A)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CV
+(3A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CV
+(3A)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CV
+(3A)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ASL
+(3A)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ASL
+(3A)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ASL
+(3A)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ASL
+(3A)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ASL
+(3A)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ASL
+(3A)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>AAI
 (3B)</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AAI
+(3B)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AAI
+(3B)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AAI
+(3B)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AAI LAB
+(3B)
+[LAB]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AAI LAB
+(3B)
+[LAB]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AAI LAB
+(3B)
+[LAB]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AAI
+(3B)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Period 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Period 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Period 3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CV
+(3B)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CV
+(3B)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CV
+(3B)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CV
+(3B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CV
+(3B)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CV
+(3B)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
